--- a/Output Files GPT-OSS 20B/LLM-Parameterized_Reference_Scoring_results_run_05.xlsx
+++ b/Output Files GPT-OSS 20B/LLM-Parameterized_Reference_Scoring_results_run_05.xlsx
@@ -38351,7 +38351,7 @@
         <v>3</v>
       </c>
       <c r="AD410" t="n">
-        <v>0.8194999999999999</v>
+        <v>0.8195</v>
       </c>
     </row>
     <row r="411">
@@ -38821,7 +38821,7 @@
         <v>3</v>
       </c>
       <c r="AD415" t="n">
-        <v>0.7509999999999999</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="416">
@@ -39479,7 +39479,7 @@
         <v>1</v>
       </c>
       <c r="AD422" t="n">
-        <v>0.6469999999999999</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="423">
@@ -39564,7 +39564,7 @@
         <v>0.58</v>
       </c>
       <c r="AA423" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="AB423" t="n">
         <v>0.52</v>
@@ -39573,7 +39573,7 @@
         <v>2</v>
       </c>
       <c r="AD423" t="n">
-        <v>0.597</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="424">
@@ -39658,7 +39658,7 @@
         <v>0.38</v>
       </c>
       <c r="AA424" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB424" t="n">
         <v>0.67</v>
@@ -39667,7 +39667,7 @@
         <v>3</v>
       </c>
       <c r="AD424" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="425">
@@ -40137,7 +40137,7 @@
         <v>2</v>
       </c>
       <c r="AD429" t="n">
-        <v>0.6469999999999999</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="430">
@@ -40222,7 +40222,7 @@
         <v>0.58</v>
       </c>
       <c r="AA430" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="AB430" t="n">
         <v>0.52</v>
@@ -40231,7 +40231,7 @@
         <v>3</v>
       </c>
       <c r="AD430" t="n">
-        <v>0.597</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="431">
@@ -40419,7 +40419,7 @@
         <v>2</v>
       </c>
       <c r="AD432" t="n">
-        <v>0.7129999999999999</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="433">
@@ -40598,7 +40598,7 @@
         <v>0.64</v>
       </c>
       <c r="AA434" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AB434" t="n">
         <v>0.46</v>
@@ -40607,7 +40607,7 @@
         <v>1</v>
       </c>
       <c r="AD434" t="n">
-        <v>0.6240000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="435">
@@ -40692,7 +40692,7 @@
         <v>0.38</v>
       </c>
       <c r="AA435" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB435" t="n">
         <v>0.67</v>
@@ -40701,7 +40701,7 @@
         <v>2</v>
       </c>
       <c r="AD435" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="436">
@@ -40786,7 +40786,7 @@
         <v>0.13</v>
       </c>
       <c r="AA436" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="AB436" t="n">
         <v>0.48</v>
@@ -40795,7 +40795,7 @@
         <v>3</v>
       </c>
       <c r="AD436" t="n">
-        <v>0.2075</v>
+        <v>0.2335</v>
       </c>
     </row>
     <row r="437">
@@ -41171,7 +41171,7 @@
         <v>1</v>
       </c>
       <c r="AD440" t="n">
-        <v>0.6469999999999999</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="441">
@@ -41256,7 +41256,7 @@
         <v>0.51</v>
       </c>
       <c r="AA441" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="AB441" t="n">
         <v>0.57</v>
@@ -41265,7 +41265,7 @@
         <v>2</v>
       </c>
       <c r="AD441" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.574</v>
       </c>
     </row>
     <row r="442">
@@ -41350,7 +41350,7 @@
         <v>0.19</v>
       </c>
       <c r="AA442" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB442" t="n">
         <v>0.52</v>
@@ -41359,7 +41359,7 @@
         <v>3</v>
       </c>
       <c r="AD442" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="443">
@@ -41547,7 +41547,7 @@
         <v>2</v>
       </c>
       <c r="AD444" t="n">
-        <v>0.6839999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="445">
@@ -41820,7 +41820,7 @@
         <v>0</v>
       </c>
       <c r="AA447" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="AB447" t="n">
         <v>0.57</v>
@@ -41829,7 +41829,7 @@
         <v>2</v>
       </c>
       <c r="AD447" t="n">
-        <v>0.2675</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="448">
@@ -41914,7 +41914,7 @@
         <v>0</v>
       </c>
       <c r="AA448" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB448" t="n">
         <v>0.52</v>
@@ -41923,7 +41923,7 @@
         <v>3</v>
       </c>
       <c r="AD448" t="n">
-        <v>0.188</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="449">
@@ -42290,7 +42290,7 @@
         <v>0.38</v>
       </c>
       <c r="AA452" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB452" t="n">
         <v>0.67</v>
@@ -42299,7 +42299,7 @@
         <v>1</v>
       </c>
       <c r="AD452" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="453">
@@ -42384,7 +42384,7 @@
         <v>0.19</v>
       </c>
       <c r="AA453" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB453" t="n">
         <v>0.52</v>
@@ -42393,7 +42393,7 @@
         <v>2</v>
       </c>
       <c r="AD453" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="454">
@@ -42478,7 +42478,7 @@
         <v>0</v>
       </c>
       <c r="AA454" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="AB454" t="n">
         <v>0.4</v>
@@ -42487,7 +42487,7 @@
         <v>3</v>
       </c>
       <c r="AD454" t="n">
-        <v>0.102</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="455">
@@ -42675,7 +42675,7 @@
         <v>1</v>
       </c>
       <c r="AD456" t="n">
-        <v>0.8815000000000001</v>
+        <v>0.8815</v>
       </c>
     </row>
     <row r="457">
@@ -42769,7 +42769,7 @@
         <v>3</v>
       </c>
       <c r="AD457" t="n">
-        <v>0.7989999999999999</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="458">
@@ -43145,7 +43145,7 @@
         <v>3</v>
       </c>
       <c r="AD461" t="n">
-        <v>0.7084999999999999</v>
+        <v>0.7085</v>
       </c>
     </row>
     <row r="462">
@@ -43239,7 +43239,7 @@
         <v>2</v>
       </c>
       <c r="AD462" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="463">
@@ -43615,7 +43615,7 @@
         <v>2</v>
       </c>
       <c r="AD466" t="n">
-        <v>0.7589999999999999</v>
+        <v>0.759</v>
       </c>
     </row>
     <row r="467">
@@ -43700,7 +43700,7 @@
         <v>0.64</v>
       </c>
       <c r="AA467" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AB467" t="n">
         <v>0.46</v>
@@ -43709,7 +43709,7 @@
         <v>1</v>
       </c>
       <c r="AD467" t="n">
-        <v>0.6240000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="468">
@@ -43794,7 +43794,7 @@
         <v>0.38</v>
       </c>
       <c r="AA468" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB468" t="n">
         <v>0.67</v>
@@ -43803,7 +43803,7 @@
         <v>2</v>
       </c>
       <c r="AD468" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="469">
@@ -43888,7 +43888,7 @@
         <v>0.19</v>
       </c>
       <c r="AA469" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB469" t="n">
         <v>0.52</v>
@@ -43897,7 +43897,7 @@
         <v>3</v>
       </c>
       <c r="AD469" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="470">
@@ -44085,7 +44085,7 @@
         <v>1</v>
       </c>
       <c r="AD471" t="n">
-        <v>0.8815000000000001</v>
+        <v>0.8815</v>
       </c>
     </row>
     <row r="472">
@@ -44179,7 +44179,7 @@
         <v>3</v>
       </c>
       <c r="AD472" t="n">
-        <v>0.7989999999999999</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="473">
@@ -44264,7 +44264,7 @@
         <v>0.51</v>
       </c>
       <c r="AA473" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="AB473" t="n">
         <v>0.15</v>
@@ -44273,7 +44273,7 @@
         <v>1</v>
       </c>
       <c r="AD473" t="n">
-        <v>0.431</v>
+        <v>0.449</v>
       </c>
     </row>
     <row r="474">
@@ -44358,7 +44358,7 @@
         <v>0.13</v>
       </c>
       <c r="AA474" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="AB474" t="n">
         <v>0.46</v>
@@ -44367,7 +44367,7 @@
         <v>3</v>
       </c>
       <c r="AD474" t="n">
-        <v>0.2725</v>
+        <v>0.2885</v>
       </c>
     </row>
     <row r="475">
@@ -44452,7 +44452,7 @@
         <v>0</v>
       </c>
       <c r="AA475" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="AB475" t="n">
         <v>0.67</v>
@@ -44461,7 +44461,7 @@
         <v>2</v>
       </c>
       <c r="AD475" t="n">
-        <v>0.2765</v>
+        <v>0.2905</v>
       </c>
     </row>
     <row r="476">
@@ -44555,7 +44555,7 @@
         <v>1</v>
       </c>
       <c r="AD476" t="n">
-        <v>0.7615000000000001</v>
+        <v>0.7615</v>
       </c>
     </row>
     <row r="477">
@@ -45016,7 +45016,7 @@
         <v>0</v>
       </c>
       <c r="AA481" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB481" t="n">
         <v>0.57</v>
@@ -45025,7 +45025,7 @@
         <v>3</v>
       </c>
       <c r="AD481" t="n">
-        <v>0.2675</v>
+        <v>0.2795</v>
       </c>
     </row>
     <row r="482">
@@ -45119,7 +45119,7 @@
         <v>2</v>
       </c>
       <c r="AD482" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="483">
@@ -45298,7 +45298,7 @@
         <v>0.58</v>
       </c>
       <c r="AA484" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="AB484" t="n">
         <v>0.52</v>
@@ -45307,7 +45307,7 @@
         <v>3</v>
       </c>
       <c r="AD484" t="n">
-        <v>0.571</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="485">
@@ -45401,7 +45401,7 @@
         <v>1</v>
       </c>
       <c r="AD485" t="n">
-        <v>0.7555000000000001</v>
+        <v>0.7554999999999999</v>
       </c>
     </row>
     <row r="486">
@@ -45495,7 +45495,7 @@
         <v>2</v>
       </c>
       <c r="AD486" t="n">
-        <v>0.6739999999999999</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="487">
@@ -45768,7 +45768,7 @@
         <v>0.38</v>
       </c>
       <c r="AA489" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="AB489" t="n">
         <v>0.67</v>
@@ -45777,7 +45777,7 @@
         <v>2</v>
       </c>
       <c r="AD489" t="n">
-        <v>0.4995000000000001</v>
+        <v>0.5135</v>
       </c>
     </row>
     <row r="490">
@@ -45862,7 +45862,7 @@
         <v>0</v>
       </c>
       <c r="AA490" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AB490" t="n">
         <v>0.32</v>
@@ -45871,7 +45871,7 @@
         <v>3</v>
       </c>
       <c r="AD490" t="n">
-        <v>0.048</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="491">
@@ -45965,7 +45965,7 @@
         <v>1</v>
       </c>
       <c r="AD491" t="n">
-        <v>0.7084999999999999</v>
+        <v>0.7085</v>
       </c>
     </row>
     <row r="492">
@@ -46153,7 +46153,7 @@
         <v>3</v>
       </c>
       <c r="AD493" t="n">
-        <v>0.3995000000000001</v>
+        <v>0.3995</v>
       </c>
     </row>
     <row r="494">
@@ -46717,7 +46717,7 @@
         <v>3</v>
       </c>
       <c r="AD499" t="n">
-        <v>0.7729999999999999</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="500">
@@ -47093,7 +47093,7 @@
         <v>2</v>
       </c>
       <c r="AD503" t="n">
-        <v>0.8164999999999999</v>
+        <v>0.8165</v>
       </c>
     </row>
     <row r="504">
@@ -47375,7 +47375,7 @@
         <v>2</v>
       </c>
       <c r="AD506" t="n">
-        <v>0.7625000000000001</v>
+        <v>0.7625</v>
       </c>
     </row>
     <row r="507">
@@ -47563,7 +47563,7 @@
         <v>3</v>
       </c>
       <c r="AD508" t="n">
-        <v>0.6200000000000001</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="509">
@@ -47742,7 +47742,7 @@
         <v>0.64</v>
       </c>
       <c r="AA510" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AB510" t="n">
         <v>0.46</v>
@@ -47751,7 +47751,7 @@
         <v>2</v>
       </c>
       <c r="AD510" t="n">
-        <v>0.6519999999999999</v>
+        <v>0.654</v>
       </c>
     </row>
     <row r="511">
@@ -47836,7 +47836,7 @@
         <v>0.38</v>
       </c>
       <c r="AA511" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="AB511" t="n">
         <v>0.67</v>
@@ -47845,7 +47845,7 @@
         <v>3</v>
       </c>
       <c r="AD511" t="n">
-        <v>0.4965000000000001</v>
+        <v>0.5125</v>
       </c>
     </row>
     <row r="512">
@@ -47930,7 +47930,7 @@
         <v>0.64</v>
       </c>
       <c r="AA512" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AB512" t="n">
         <v>0.46</v>
@@ -47939,7 +47939,7 @@
         <v>1</v>
       </c>
       <c r="AD512" t="n">
-        <v>0.665</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="513">
@@ -48024,7 +48024,7 @@
         <v>0.51</v>
       </c>
       <c r="AA513" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB513" t="n">
         <v>0.57</v>
@@ -48033,7 +48033,7 @@
         <v>2</v>
       </c>
       <c r="AD513" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="514">
@@ -48118,7 +48118,7 @@
         <v>0.38</v>
       </c>
       <c r="AA514" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="AB514" t="n">
         <v>0.67</v>
@@ -48127,7 +48127,7 @@
         <v>3</v>
       </c>
       <c r="AD514" t="n">
-        <v>0.5065000000000001</v>
+        <v>0.5185</v>
       </c>
     </row>
     <row r="515">
@@ -48306,7 +48306,7 @@
         <v>0.51</v>
       </c>
       <c r="AA516" t="n">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="AB516" t="n">
         <v>0.57</v>
@@ -48315,7 +48315,7 @@
         <v>2</v>
       </c>
       <c r="AD516" t="n">
-        <v>0.5950000000000001</v>
+        <v>0.609</v>
       </c>
     </row>
     <row r="517">
@@ -48400,7 +48400,7 @@
         <v>0.38</v>
       </c>
       <c r="AA517" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="AB517" t="n">
         <v>0.67</v>
@@ -48409,7 +48409,7 @@
         <v>3</v>
       </c>
       <c r="AD517" t="n">
-        <v>0.4995000000000001</v>
+        <v>0.5135</v>
       </c>
     </row>
     <row r="518">
@@ -48494,7 +48494,7 @@
         <v>0.72</v>
       </c>
       <c r="AA518" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AB518" t="n">
         <v>0.46</v>
@@ -48503,7 +48503,7 @@
         <v>1</v>
       </c>
       <c r="AD518" t="n">
-        <v>0.7270000000000001</v>
+        <v>0.729</v>
       </c>
     </row>
     <row r="519">
@@ -48588,7 +48588,7 @@
         <v>0.62</v>
       </c>
       <c r="AA519" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="AB519" t="n">
         <v>0.57</v>
@@ -48597,7 +48597,7 @@
         <v>2</v>
       </c>
       <c r="AD519" t="n">
-        <v>0.6745000000000001</v>
+        <v>0.6845</v>
       </c>
     </row>
     <row r="520">
@@ -48682,7 +48682,7 @@
         <v>0.51</v>
       </c>
       <c r="AA520" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="AB520" t="n">
         <v>0.67</v>
@@ -48691,7 +48691,7 @@
         <v>3</v>
       </c>
       <c r="AD520" t="n">
-        <v>0.5970000000000001</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="521">
@@ -48776,7 +48776,7 @@
         <v>0.85</v>
       </c>
       <c r="AA521" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AB521" t="n">
         <v>0.46</v>
@@ -48785,7 +48785,7 @@
         <v>1</v>
       </c>
       <c r="AD521" t="n">
-        <v>0.7985</v>
+        <v>0.8005</v>
       </c>
     </row>
     <row r="522">
@@ -48870,7 +48870,7 @@
         <v>0.77</v>
       </c>
       <c r="AA522" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB522" t="n">
         <v>0.57</v>
@@ -48879,7 +48879,7 @@
         <v>2</v>
       </c>
       <c r="AD522" t="n">
-        <v>0.768</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="523">
@@ -48964,7 +48964,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA523" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="AB523" t="n">
         <v>0.67</v>
@@ -48973,7 +48973,7 @@
         <v>3</v>
       </c>
       <c r="AD523" t="n">
-        <v>0.7050000000000001</v>
+        <v>0.717</v>
       </c>
     </row>
     <row r="524">
@@ -49152,7 +49152,7 @@
         <v>0.62</v>
       </c>
       <c r="AA525" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AB525" t="n">
         <v>0.57</v>
@@ -49161,7 +49161,7 @@
         <v>2</v>
       </c>
       <c r="AD525" t="n">
-        <v>0.6735000000000001</v>
+        <v>0.6815</v>
       </c>
     </row>
     <row r="526">
@@ -49246,7 +49246,7 @@
         <v>0.51</v>
       </c>
       <c r="AA526" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="AB526" t="n">
         <v>0.67</v>
@@ -49255,7 +49255,7 @@
         <v>3</v>
       </c>
       <c r="AD526" t="n">
-        <v>0.5940000000000001</v>
+        <v>0.604</v>
       </c>
     </row>
     <row r="527">
@@ -49443,7 +49443,7 @@
         <v>2</v>
       </c>
       <c r="AD528" t="n">
-        <v>0.6260000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="529">
@@ -49819,7 +49819,7 @@
         <v>3</v>
       </c>
       <c r="AD532" t="n">
-        <v>0.7509999999999999</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="533">
@@ -50007,7 +50007,7 @@
         <v>2</v>
       </c>
       <c r="AD534" t="n">
-        <v>0.6260000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="535">
@@ -50289,7 +50289,7 @@
         <v>2</v>
       </c>
       <c r="AD537" t="n">
-        <v>0.7609999999999999</v>
+        <v>0.761</v>
       </c>
     </row>
     <row r="538">
@@ -50477,7 +50477,7 @@
         <v>1</v>
       </c>
       <c r="AD539" t="n">
-        <v>0.7344999999999999</v>
+        <v>0.7345</v>
       </c>
     </row>
     <row r="540">
@@ -50665,7 +50665,7 @@
         <v>3</v>
       </c>
       <c r="AD541" t="n">
-        <v>0.6339999999999999</v>
+        <v>0.634</v>
       </c>
     </row>
     <row r="542">
@@ -50938,7 +50938,7 @@
         <v>0.51</v>
       </c>
       <c r="AA544" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="AB544" t="n">
         <v>0.57</v>
@@ -50947,7 +50947,7 @@
         <v>3</v>
       </c>
       <c r="AD544" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="545">
@@ -51041,7 +51041,7 @@
         <v>3</v>
       </c>
       <c r="AD545" t="n">
-        <v>0.6764999999999999</v>
+        <v>0.6765</v>
       </c>
     </row>
     <row r="546">
@@ -51135,7 +51135,7 @@
         <v>1</v>
       </c>
       <c r="AD546" t="n">
-        <v>0.8270000000000001</v>
+        <v>0.827</v>
       </c>
     </row>
     <row r="547">
@@ -51323,7 +51323,7 @@
         <v>1</v>
       </c>
       <c r="AD548" t="n">
-        <v>0.7374999999999999</v>
+        <v>0.7375</v>
       </c>
     </row>
     <row r="549">
@@ -52075,7 +52075,7 @@
         <v>3</v>
       </c>
       <c r="AD556" t="n">
-        <v>0.5455000000000001</v>
+        <v>0.5455</v>
       </c>
     </row>
     <row r="557">
@@ -52169,7 +52169,7 @@
         <v>1</v>
       </c>
       <c r="AD557" t="n">
-        <v>0.6769999999999999</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="558">
@@ -52254,7 +52254,7 @@
         <v>0.64</v>
       </c>
       <c r="AA558" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AB558" t="n">
         <v>0.46</v>
@@ -52263,7 +52263,7 @@
         <v>2</v>
       </c>
       <c r="AD558" t="n">
-        <v>0.665</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="559">
@@ -52348,7 +52348,7 @@
         <v>0.51</v>
       </c>
       <c r="AA559" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB559" t="n">
         <v>0.57</v>
@@ -52357,7 +52357,7 @@
         <v>3</v>
       </c>
       <c r="AD559" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="560">
@@ -52536,7 +52536,7 @@
         <v>0.51</v>
       </c>
       <c r="AA561" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AB561" t="n">
         <v>0.57</v>
@@ -52545,7 +52545,7 @@
         <v>2</v>
       </c>
       <c r="AD561" t="n">
-        <v>0.6080000000000001</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="562">
@@ -52630,7 +52630,7 @@
         <v>0.38</v>
       </c>
       <c r="AA562" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="AB562" t="n">
         <v>0.67</v>
@@ -52639,7 +52639,7 @@
         <v>3</v>
       </c>
       <c r="AD562" t="n">
-        <v>0.5155000000000001</v>
+        <v>0.5255</v>
       </c>
     </row>
     <row r="563">
@@ -52921,7 +52921,7 @@
         <v>3</v>
       </c>
       <c r="AD565" t="n">
-        <v>0.7509999999999999</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="566">
@@ -53015,7 +53015,7 @@
         <v>3</v>
       </c>
       <c r="AD566" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="567">
@@ -53203,7 +53203,7 @@
         <v>1</v>
       </c>
       <c r="AD568" t="n">
-        <v>0.8624999999999999</v>
+        <v>0.8625</v>
       </c>
     </row>
     <row r="569">
@@ -53485,7 +53485,7 @@
         <v>3</v>
       </c>
       <c r="AD571" t="n">
-        <v>0.7149999999999999</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="572">
@@ -53579,7 +53579,7 @@
         <v>1</v>
       </c>
       <c r="AD572" t="n">
-        <v>0.7649999999999999</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="573">
@@ -53767,7 +53767,7 @@
         <v>3</v>
       </c>
       <c r="AD574" t="n">
-        <v>0.7069999999999999</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="575">
@@ -53861,7 +53861,7 @@
         <v>1</v>
       </c>
       <c r="AD575" t="n">
-        <v>0.7589999999999999</v>
+        <v>0.759</v>
       </c>
     </row>
     <row r="576">
@@ -54143,7 +54143,7 @@
         <v>3</v>
       </c>
       <c r="AD578" t="n">
-        <v>0.7994999999999999</v>
+        <v>0.7995</v>
       </c>
     </row>
     <row r="579">
@@ -54237,7 +54237,7 @@
         <v>1</v>
       </c>
       <c r="AD579" t="n">
-        <v>0.8059999999999999</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="580">
@@ -54331,7 +54331,7 @@
         <v>2</v>
       </c>
       <c r="AD580" t="n">
-        <v>0.8029999999999999</v>
+        <v>0.803</v>
       </c>
     </row>
     <row r="581">
@@ -54425,7 +54425,7 @@
         <v>3</v>
       </c>
       <c r="AD581" t="n">
-        <v>0.8074999999999999</v>
+        <v>0.8075</v>
       </c>
     </row>
     <row r="582">
@@ -54519,7 +54519,7 @@
         <v>1</v>
       </c>
       <c r="AD582" t="n">
-        <v>0.8170000000000001</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="583">
@@ -54613,7 +54613,7 @@
         <v>2</v>
       </c>
       <c r="AD583" t="n">
-        <v>0.8139999999999998</v>
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="584">
@@ -54707,7 +54707,7 @@
         <v>3</v>
       </c>
       <c r="AD584" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="585">
